--- a/experiments/results/resnet_imagenet34/ImageNet-1K/ReAct/adaptive/std/results.xlsx
+++ b/experiments/results/resnet_imagenet34/ImageNet-1K/ReAct/adaptive/std/results.xlsx
@@ -342,7 +342,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K16"/>
+  <dimension ref="A1:K19"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="61.33203125" customWidth="1" style="3" min="11" max="11"/>
@@ -947,6 +947,117 @@
       <c r="K16" s="4" t="inlineStr">
         <is>
           <t>dice_p=None,ash_p=None,react_th=2.0,scale_th=0.35,type=std</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="n">
+        <v>23.98</v>
+      </c>
+      <c r="B17" s="4" t="n">
+        <v>94.92</v>
+      </c>
+      <c r="C17" s="4" t="n">
+        <v>35.13</v>
+      </c>
+      <c r="D17" s="4" t="n">
+        <v>92.20999999999999</v>
+      </c>
+      <c r="E17" s="4" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="F17" s="4" t="n">
+        <v>97.44</v>
+      </c>
+      <c r="G17" s="4" t="n">
+        <v>13.54</v>
+      </c>
+      <c r="H17" s="4" t="n">
+        <v>97.41</v>
+      </c>
+      <c r="I17" s="4" t="n">
+        <v>21.14</v>
+      </c>
+      <c r="J17" s="4" t="n">
+        <v>95.5</v>
+      </c>
+      <c r="K17" s="4" t="inlineStr">
+        <is>
+          <t>dice_p=None,ash_p=None,react_th=2.0,scale_th=0.5,type=std</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="n">
+        <v>23.35</v>
+      </c>
+      <c r="B18" s="4" t="n">
+        <v>94.94</v>
+      </c>
+      <c r="C18" s="4" t="n">
+        <v>34.22</v>
+      </c>
+      <c r="D18" s="4" t="n">
+        <v>92.23999999999999</v>
+      </c>
+      <c r="E18" s="4" t="n">
+        <v>11.86</v>
+      </c>
+      <c r="F18" s="4" t="n">
+        <v>97.41</v>
+      </c>
+      <c r="G18" s="4" t="n">
+        <v>12.87</v>
+      </c>
+      <c r="H18" s="4" t="n">
+        <v>97.42</v>
+      </c>
+      <c r="I18" s="4" t="n">
+        <v>20.58</v>
+      </c>
+      <c r="J18" s="4" t="n">
+        <v>95.5</v>
+      </c>
+      <c r="K18" s="4" t="inlineStr">
+        <is>
+          <t>dice_p=None,ash_p=None,react_th=2.1,scale_th=0.5,type=std</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="n">
+        <v>23.08</v>
+      </c>
+      <c r="B19" s="4" t="n">
+        <v>94.92</v>
+      </c>
+      <c r="C19" s="4" t="n">
+        <v>33.82</v>
+      </c>
+      <c r="D19" s="4" t="n">
+        <v>92.23</v>
+      </c>
+      <c r="E19" s="4" t="n">
+        <v>11.91</v>
+      </c>
+      <c r="F19" s="4" t="n">
+        <v>97.38</v>
+      </c>
+      <c r="G19" s="4" t="n">
+        <v>12.95</v>
+      </c>
+      <c r="H19" s="4" t="n">
+        <v>97.41</v>
+      </c>
+      <c r="I19" s="4" t="n">
+        <v>20.44</v>
+      </c>
+      <c r="J19" s="4" t="n">
+        <v>95.48</v>
+      </c>
+      <c r="K19" s="4" t="inlineStr">
+        <is>
+          <t>dice_p=None,ash_p=None,react_th=2.2,scale_th=0.5,type=std</t>
         </is>
       </c>
     </row>
